--- a/quizzes/005_pcb_design_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/005_pcb_design_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1115,17 +1115,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>design_rules_choices</t>
+          <t>board_type_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>printed_wiring_boards</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Printed wiring boards</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>printed_wiring_boards</t>
+          <t>flexible_boards</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Printed wiring boards</t>
+          <t>Flexible boards</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>flexible_boards</t>
+          <t>rigid_boards</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Flexible boards</t>
+          <t>Rigid boards</t>
         </is>
       </c>
     </row>
@@ -1171,29 +1171,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rigid_boards</t>
+          <t>hybrid_boards</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rigid boards</t>
+          <t>Hybrid boards</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>board_type_choices</t>
+          <t>materials_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hybrid_boards</t>
+          <t>fr4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hybrid boards</t>
+          <t>FR4</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fr4</t>
+          <t>fr5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FR4</t>
+          <t>FR5</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fr5</t>
+          <t>fr6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FR5</t>
+          <t>FR6</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fr6</t>
+          <t>fr7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FR6</t>
+          <t>FR7</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fr7</t>
+          <t>fr8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FR7</t>
+          <t>FR8</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>fr8</t>
+          <t>fr9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FR8</t>
+          <t>FR9</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>fr9</t>
+          <t>fr10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FR9</t>
+          <t>FR10</t>
         </is>
       </c>
     </row>
@@ -1307,29 +1307,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fr10</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FR10</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>materials_choices</t>
+          <t>layer_count_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>single_layer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Single layer</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>single_layer</t>
+          <t>double_layer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Single layer</t>
+          <t>Double layer</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>double_layer</t>
+          <t>multi-layer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Double layer</t>
+          <t>Multi-layer</t>
         </is>
       </c>
     </row>
@@ -1375,29 +1375,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>multi-layer</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Multi-layer</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>layer_count_choices</t>
+          <t>design_tools_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>kicad</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kicad</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kicad</t>
+          <t>eagle</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kicad</t>
+          <t>Eagle</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eagle</t>
+          <t>altium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Altium</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>altium</t>
+          <t>kicad</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Altium</t>
+          <t>KiCad</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>kicad</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KiCad</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>autodesk_eagle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Autodesk Eagle</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>autodesk_eagle</t>
+          <t>altium_designer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Autodesk Eagle</t>
+          <t>Altium Designer</t>
         </is>
       </c>
     </row>
@@ -1511,63 +1511,63 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>altium</t>
+          <t>altium_nexus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Altium</t>
+          <t>Altium NEXUS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>design_tools_choices</t>
+          <t>design_process_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>altium_designer</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Altium Designer</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>design_tools_choices</t>
+          <t>design_process_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>altium_nexus</t>
+          <t>automated</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Altium NEXUS</t>
+          <t>Automated</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>design_tools_choices</t>
+          <t>design_process_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>top_down</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Top down</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>automated</t>
+          <t>bottom_up</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Bottom up</t>
         </is>
       </c>
     </row>
@@ -1613,61 +1613,10 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>design_process_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>top_down</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Top down</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>design_process_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>bottom_up</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Bottom up</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>design_process_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
